--- a/Data/Transfer.xlsx
+++ b/Data/Transfer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclipse\Desktop\Automation-Testing-2025\Eclipse\Automation\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34C24A8-423E-4974-9289-EBD7336AC56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4F180C-5A07-47FB-94CD-0DC6E1D155DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="12420" yWindow="2295" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transfer_Request" sheetId="1" r:id="rId1"/>

--- a/Data/Transfer.xlsx
+++ b/Data/Transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4F180C-5A07-47FB-94CD-0DC6E1D155DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78872BDF-84A5-4300-AE25-2AAD1C6A9EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="12420" yWindow="2295" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transfer_Request" sheetId="1" r:id="rId1"/>

--- a/Data/Transfer.xlsx
+++ b/Data/Transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78872BDF-84A5-4300-AE25-2AAD1C6A9EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DBC407-B714-42CB-A9E3-90B5C2D5A9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transfer_Request" sheetId="1" r:id="rId1"/>
@@ -461,22 +461,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>3456790</v>
+        <v>26022026</v>
       </c>
       <c r="B2" s="4">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="C2" s="4">
-        <v>1000421</v>
+        <v>8888888</v>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="E2" s="7">
-        <v>100673000000011</v>
+        <v>178888880001601</v>
       </c>
       <c r="F2" s="7">
-        <v>120733340001420</v>
+        <v>126220260000016</v>
       </c>
       <c r="G2" s="7">
         <v>110001023032</v>

--- a/Data/Transfer.xlsx
+++ b/Data/Transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DBC407-B714-42CB-A9E3-90B5C2D5A9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF46743-8EAA-4C8B-93FB-15359482031B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="12375" yWindow="2295" windowWidth="8565" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transfer_Request" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -86,12 +86,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -129,16 +123,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,37 +453,37 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>26022026</v>
-      </c>
-      <c r="B2" s="4">
-        <v>8888999</v>
-      </c>
-      <c r="C2" s="4">
-        <v>8888888</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1003</v>
-      </c>
-      <c r="E2" s="7">
-        <v>178888880001601</v>
-      </c>
-      <c r="F2" s="7">
-        <v>126220260000016</v>
-      </c>
-      <c r="G2" s="7">
-        <v>110001023032</v>
-      </c>
-      <c r="H2" s="5">
-        <v>100</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="A2" s="1">
+        <v>1062029</v>
+      </c>
+      <c r="B2" s="5">
+        <v>6656413</v>
+      </c>
+      <c r="C2" s="5">
+        <v>6539191</v>
+      </c>
+      <c r="D2" s="5">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6">
+        <v>120484000000134</v>
+      </c>
+      <c r="F2" s="6">
+        <v>120484000001264</v>
+      </c>
+      <c r="G2" s="6">
+        <v>110001509824</v>
+      </c>
+      <c r="H2" s="7">
+        <v>100</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>3456791</v>
+        <v>1062029</v>
       </c>
       <c r="B3" s="1">
         <v>9999996</v>
@@ -501,13 +494,13 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>110001024279</v>
       </c>
       <c r="H3" s="2">
@@ -518,7 +511,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="5">
         <v>3456792</v>
       </c>
       <c r="B4" s="1">
@@ -530,13 +523,13 @@
       <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>110001024238</v>
       </c>
       <c r="H4" s="2">
@@ -559,13 +552,13 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>110001024253</v>
       </c>
       <c r="H5" s="2">
@@ -576,7 +569,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="5">
         <v>3456794</v>
       </c>
       <c r="B6" s="1">
@@ -588,13 +581,13 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>110001024295</v>
       </c>
       <c r="H6" s="2">
@@ -605,36 +598,36 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>3456795</v>
-      </c>
-      <c r="B7" s="1">
-        <v>9999996</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1000421</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
+      <c r="A7" s="5">
+        <v>26022026</v>
+      </c>
+      <c r="B7" s="5">
+        <v>8888999</v>
+      </c>
+      <c r="C7" s="5">
+        <v>8888888</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1003</v>
       </c>
       <c r="E7" s="6">
-        <v>100673000000011</v>
+        <v>178888880001601</v>
       </c>
       <c r="F7" s="6">
-        <v>120733340001420</v>
+        <v>126220260000016</v>
       </c>
       <c r="G7" s="6">
-        <v>110001024394</v>
-      </c>
-      <c r="H7" s="2">
-        <v>100</v>
-      </c>
-      <c r="I7" s="1" t="s">
+        <v>110001023032</v>
+      </c>
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="5">
         <v>3456796</v>
       </c>
       <c r="B8" s="1">
@@ -646,13 +639,13 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>110001024410</v>
       </c>
       <c r="H8" s="2">
@@ -675,13 +668,13 @@
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>100673000000011</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>120733340001420</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>110001024436</v>
       </c>
       <c r="H9" s="2">
